--- a/data/C_100_1000K.xlsx
+++ b/data/C_100_1000K.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\CC_scripts\Shermo_post\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrc\Desktop\ThermoCR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D086506B-8935-43FC-8891-7BC7E943E79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659F1BFF-F282-4AC4-82C1-E1B3121FF3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -299,11 +288,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T(K)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>INFINITE</t>
   </si>
   <si>
-    <t>INFINITE</t>
+    <t>T/K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -669,11 +658,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -700,7 +689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -711,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
         <v>-6.5359999999999996</v>
@@ -723,13 +712,13 @@
         <v>711.18499999999995</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>100</v>
       </c>
@@ -759,7 +748,7 @@
         <v>134.23000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>200</v>
       </c>
@@ -789,7 +778,7 @@
         <v>146.68499999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>250</v>
       </c>
@@ -819,7 +808,7 @@
         <v>150.0319999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>298.14999999999998</v>
       </c>
@@ -849,7 +838,7 @@
         <v>152.35955056179753</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>300</v>
       </c>
@@ -879,7 +868,7 @@
         <v>152.43666666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>350</v>
       </c>
@@ -909,7 +898,7 @@
         <v>154.19714285714301</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>400</v>
       </c>
@@ -939,7 +928,7 @@
         <v>155.505</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>450</v>
       </c>
@@ -969,7 +958,7 @@
         <v>156.47999999999988</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>500</v>
       </c>
@@ -999,7 +988,7 @@
         <v>157.202</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>600</v>
       </c>
@@ -1029,7 +1018,7 @@
         <v>158.12333333333339</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>700</v>
       </c>
@@ -1059,7 +1048,7 @@
         <v>158.59857142857143</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>800</v>
       </c>
@@ -1089,7 +1078,7 @@
         <v>158.81250000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>900</v>
       </c>
@@ -1119,7 +1108,7 @@
         <v>158.8666666666667</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1000</v>
       </c>
@@ -1149,7 +1138,7 @@
         <v>158.82100000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1159,7 +1148,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1169,7 +1158,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1179,7 +1168,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1189,7 +1178,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1199,7 +1188,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1209,7 +1198,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1219,7 +1208,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1229,7 +1218,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1239,7 +1228,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1249,7 +1238,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1259,7 +1248,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1269,7 +1258,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1279,7 +1268,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1289,7 +1278,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1299,7 +1288,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1309,7 +1298,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1319,7 +1308,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1329,7 +1318,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1339,7 +1328,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1349,7 +1338,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1359,7 +1348,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1369,7 +1358,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1379,7 +1368,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1389,7 +1378,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1399,7 +1388,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1409,7 +1398,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1419,7 +1408,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1429,7 +1418,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1439,7 +1428,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1449,7 +1438,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1459,7 +1448,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1469,7 +1458,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1479,7 +1468,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1489,7 +1478,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1499,7 +1488,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
